--- a/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
+++ b/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>ワークショップキット（スノードーム/スクイーズ/チャーム）</t>
+          <t>ワークショップキット（スノードーム/スクイーズ）</t>
         </is>
       </c>
       <c r="C18" s="78" t="n"/>
@@ -1388,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="H18" s="34" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B19" s="79" t="inlineStr">
         <is>
-          <t>エア遊具1点＋クリスマスアーチ（期間中レンタル）</t>
+          <t>販促物一式（クリスマスアーチ・B0ポスター10枚・開催中ツール・コスプレ）</t>
         </is>
       </c>
       <c r="C19" s="78" t="n"/>
@@ -1416,14 +1416,14 @@
         <v>1</v>
       </c>
       <c r="F19" s="37" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G19" s="37" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="H19" s="38" t="inlineStr">
         <is>
-          <t>期間終了後に返却</t>
+          <t>アーチは期間中レンタル・終了後返却</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B20" s="80" t="inlineStr">
         <is>
-          <t>販促物一式（B0ポスター10枚・開催中ツール・コスプレ）</t>
+          <t>企画・ディレクション・運用マニュアル</t>
         </is>
       </c>
       <c r="C20" s="78" t="n"/>
@@ -1444,39 +1444,23 @@
         <v>1</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>800000</v>
-      </c>
-      <c r="H20" s="40" t="inlineStr">
-        <is>
-          <t>コスプレ：サンタ・雪だるま・トナカイ</t>
-        </is>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="H20" s="40" t="n"/>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="67">
       <c r="A21" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="79" t="inlineStr">
-        <is>
-          <t>企画・ディレクション・運用マニュアル</t>
-        </is>
-      </c>
+      <c r="B21" s="79" t="n"/>
       <c r="C21" s="78" t="n"/>
-      <c r="D21" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="42" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G21" s="42" t="n">
-        <v>200000</v>
-      </c>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
       <c r="H21" s="40" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="67">

--- a/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
+++ b/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
@@ -1312,7 +1312,7 @@
     <row r="15" ht="20.25" customHeight="1" s="67">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>実施期間：2026年12月 4週間（日程別途調整）</t>
+          <t>実施期間：2026年11月28日～2026年12月25日（4週間）</t>
         </is>
       </c>
       <c r="B15" s="1" t="n"/>

--- a/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
+++ b/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B20" s="80" t="inlineStr">
         <is>
-          <t>企画・ディレクション・運用マニュアル</t>
+          <t>管理運営費</t>
         </is>
       </c>
       <c r="C20" s="78" t="n"/>

--- a/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
+++ b/docs/proposals/2026-12_docomo_christmas-ws/御見積書_NTTドコモ_クリスマスWS.xlsx
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>ワークショップキット（スノードーム/スクイーズ）</t>
+          <t>スノードームキット（第1・4週）</t>
         </is>
       </c>
       <c r="C18" s="78" t="n"/>
@@ -1388,14 +1388,14 @@
         <v>1</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="H18" s="34" t="inlineStr">
         <is>
-          <t>1地区300個/週×4週=1,200個</t>
+          <t>1地区300個/週×2週=600個</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B19" s="79" t="inlineStr">
         <is>
-          <t>販促物一式（クリスマスアーチ・B0ポスター10枚・開催中ツール・コスプレ）</t>
+          <t>スクイーズキット（第2・3週）</t>
         </is>
       </c>
       <c r="C19" s="78" t="n"/>
@@ -1416,14 +1416,14 @@
         <v>1</v>
       </c>
       <c r="F19" s="37" t="n">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="G19" s="37" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="H19" s="38" t="inlineStr">
         <is>
-          <t>アーチは期間中レンタル・終了後返却</t>
+          <t>1地区300個/週×2週=600個</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B20" s="80" t="inlineStr">
         <is>
-          <t>管理運営費</t>
+          <t>販促物一式（クリスマスアーチ・B0ポスター10枚・開催中ツール・コスプレ）</t>
         </is>
       </c>
       <c r="C20" s="78" t="n"/>
@@ -1444,23 +1444,39 @@
         <v>1</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H20" s="40" t="n"/>
+        <v>800000</v>
+      </c>
+      <c r="H20" s="40" t="inlineStr">
+        <is>
+          <t>アーチは期間中レンタル・終了後返却</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="67">
       <c r="A21" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="79" t="n"/>
+      <c r="B21" s="79" t="inlineStr">
+        <is>
+          <t>管理運営費</t>
+        </is>
+      </c>
       <c r="C21" s="78" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="42" t="n"/>
-      <c r="G21" s="42" t="n"/>
+      <c r="D21" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>200000</v>
+      </c>
       <c r="H21" s="40" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="67">
